--- a/artfynd/A 18772-2026 artfynd.xlsx
+++ b/artfynd/A 18772-2026 artfynd.xlsx
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67525753</v>
+        <v>75378652</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>706</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Geranium bohemicum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljusa bergen, Upl</t>
+          <t>Mellan Nysättra och Alphyddan, vid vägen, S om bommen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654390.1161474221</v>
+        <v>654478</v>
       </c>
       <c r="R2" t="n">
-        <v>6607032.277854675</v>
+        <v>6607141</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Många längs vägkanten.</t>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,63 +762,75 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>grusgrop</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Irebrand</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Irebrand</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75378652</v>
+        <v>67525753</v>
       </c>
       <c r="B3" t="n">
-        <v>104094</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>706</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellan Nysättra och Alphyddan, vid vägen, S om bommen, Upl</t>
+          <t>Ljusa bergen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654478</v>
+        <v>654390</v>
       </c>
       <c r="R3" t="n">
-        <v>6607141</v>
+        <v>6607032</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +854,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>2017-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1998-12-31</t>
+          <t>2017-06-25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>Många längs vägkanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,27 +876,18 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>grusgrop</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Linda Irebrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Linda Irebrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
